--- a/artfynd/A 21326-2026 artfynd.xlsx
+++ b/artfynd/A 21326-2026 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134067281</v>
+        <v>134067285</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>89340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441484</v>
+        <v>441611</v>
       </c>
       <c r="R6" t="n">
-        <v>7001581</v>
+        <v>7001450</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134067285</v>
+        <v>134067281</v>
       </c>
       <c r="B7" t="n">
-        <v>89340</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441611</v>
+        <v>441484</v>
       </c>
       <c r="R7" t="n">
-        <v>7001450</v>
+        <v>7001581</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1854,7 +1854,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134374962</v>
+        <v>134374965</v>
       </c>
       <c r="B14" t="n">
         <v>79359</v>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441503</v>
+        <v>441603</v>
       </c>
       <c r="R14" t="n">
-        <v>7001567</v>
+        <v>7001485</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134374965</v>
+        <v>134374962</v>
       </c>
       <c r="B15" t="n">
         <v>79359</v>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441603</v>
+        <v>441503</v>
       </c>
       <c r="R15" t="n">
-        <v>7001485</v>
+        <v>7001567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134374971</v>
+        <v>134374951</v>
       </c>
       <c r="B22" t="n">
-        <v>83208</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441588</v>
+        <v>441506</v>
       </c>
       <c r="R22" t="n">
-        <v>7001518</v>
+        <v>7001559</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,6 +2716,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,10 +2747,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134374974</v>
+        <v>134374971</v>
       </c>
       <c r="B23" t="n">
-        <v>89340</v>
+        <v>83208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,21 +2758,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441513</v>
+        <v>441588</v>
       </c>
       <c r="R23" t="n">
-        <v>7001578</v>
+        <v>7001518</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2844,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134374959</v>
+        <v>134374974</v>
       </c>
       <c r="B24" t="n">
-        <v>91974</v>
+        <v>89340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2855,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441508</v>
+        <v>441513</v>
       </c>
       <c r="R24" t="n">
-        <v>7001539</v>
+        <v>7001578</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134374951</v>
+        <v>134374959</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441506</v>
+        <v>441508</v>
       </c>
       <c r="R25" t="n">
-        <v>7001559</v>
+        <v>7001539</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3007,11 +3012,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3038,7 +3038,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134374969</v>
+        <v>134374964</v>
       </c>
       <c r="B26" t="n">
         <v>79359</v>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441551</v>
+        <v>441533</v>
       </c>
       <c r="R26" t="n">
-        <v>7001508</v>
+        <v>7001545</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,6 +3109,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3135,7 +3140,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134374964</v>
+        <v>134374969</v>
       </c>
       <c r="B27" t="n">
         <v>79359</v>
@@ -3170,10 +3175,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441533</v>
+        <v>441551</v>
       </c>
       <c r="R27" t="n">
-        <v>7001545</v>
+        <v>7001508</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,11 +3211,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3237,32 +3237,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134374955</v>
+        <v>134374967</v>
       </c>
       <c r="B28" t="n">
-        <v>99203</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441538</v>
+        <v>441623</v>
       </c>
       <c r="R28" t="n">
-        <v>7001492</v>
+        <v>7001479</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,6 +3308,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3334,32 +3339,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134374967</v>
+        <v>134374955</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>99203</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441623</v>
+        <v>441538</v>
       </c>
       <c r="R29" t="n">
-        <v>7001479</v>
+        <v>7001492</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,11 +3410,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 21326-2026 artfynd.xlsx
+++ b/artfynd/A 21326-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134067270</v>
       </c>
       <c r="B2" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>134067268</v>
       </c>
       <c r="B3" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>134067283</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>134067282</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>134067285</v>
       </c>
       <c r="B6" t="n">
-        <v>89340</v>
+        <v>89347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>134067281</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>134067279</v>
       </c>
       <c r="B8" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>134067267</v>
       </c>
       <c r="B9" t="n">
-        <v>92153</v>
+        <v>92160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>134067272</v>
       </c>
       <c r="B10" t="n">
-        <v>92185</v>
+        <v>92192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>134067269</v>
       </c>
       <c r="B11" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>134067284</v>
       </c>
       <c r="B12" t="n">
-        <v>89340</v>
+        <v>89347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>134374945</v>
       </c>
       <c r="B13" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>134374965</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134374962</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>134374961</v>
       </c>
       <c r="B16" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>134374948</v>
       </c>
       <c r="B17" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>134374970</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>134374946</v>
       </c>
       <c r="B19" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134374947</v>
+        <v>134374956</v>
       </c>
       <c r="B20" t="n">
-        <v>91960</v>
+        <v>99092</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441572</v>
+        <v>441546</v>
       </c>
       <c r="R20" t="n">
-        <v>7001497</v>
+        <v>7001525</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134374956</v>
+        <v>134374947</v>
       </c>
       <c r="B21" t="n">
-        <v>99085</v>
+        <v>91967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441546</v>
+        <v>441572</v>
       </c>
       <c r="R21" t="n">
-        <v>7001525</v>
+        <v>7001497</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2747,10 +2747,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134374971</v>
+        <v>134374974</v>
       </c>
       <c r="B23" t="n">
-        <v>83208</v>
+        <v>89347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441588</v>
+        <v>441513</v>
       </c>
       <c r="R23" t="n">
-        <v>7001518</v>
+        <v>7001578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134374974</v>
+        <v>134374971</v>
       </c>
       <c r="B24" t="n">
-        <v>89340</v>
+        <v>83215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2855,21 +2855,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441513</v>
+        <v>441588</v>
       </c>
       <c r="R24" t="n">
-        <v>7001578</v>
+        <v>7001518</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2944,7 +2944,7 @@
         <v>134374959</v>
       </c>
       <c r="B25" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>134374964</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>134374969</v>
       </c>
       <c r="B27" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,32 +3237,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134374967</v>
+        <v>134374955</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>99210</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441623</v>
+        <v>441538</v>
       </c>
       <c r="R28" t="n">
-        <v>7001479</v>
+        <v>7001492</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,11 +3308,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3339,32 +3334,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134374955</v>
+        <v>134374967</v>
       </c>
       <c r="B29" t="n">
-        <v>99203</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441538</v>
+        <v>441623</v>
       </c>
       <c r="R29" t="n">
-        <v>7001492</v>
+        <v>7001479</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3410,6 +3405,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3439,7 +3439,7 @@
         <v>134374949</v>
       </c>
       <c r="B30" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>134374944</v>
       </c>
       <c r="B31" t="n">
-        <v>92153</v>
+        <v>92160</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 21326-2026 artfynd.xlsx
+++ b/artfynd/A 21326-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134067270</v>
+        <v>134067284</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441623</v>
+        <v>441493</v>
       </c>
       <c r="R2" t="n">
-        <v>7001463</v>
+        <v>7001527</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134067268</v>
+        <v>134067285</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>89354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441492</v>
+        <v>441611</v>
       </c>
       <c r="R3" t="n">
-        <v>7001519</v>
+        <v>7001450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134067283</v>
+        <v>134374974</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>89354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västerfjället Ö, Jmt</t>
+          <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441541</v>
+        <v>441513</v>
       </c>
       <c r="R4" t="n">
-        <v>7001487</v>
+        <v>7001578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134067282</v>
+        <v>134374957</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västerfjället Ö, Jmt</t>
+          <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441505</v>
+        <v>441473</v>
       </c>
       <c r="R5" t="n">
-        <v>7001580</v>
+        <v>7001544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,17 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134067285</v>
+        <v>134067268</v>
       </c>
       <c r="B6" t="n">
-        <v>89347</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441611</v>
+        <v>441492</v>
       </c>
       <c r="R6" t="n">
-        <v>7001450</v>
+        <v>7001519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134067281</v>
+        <v>134067269</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441484</v>
+        <v>441481</v>
       </c>
       <c r="R7" t="n">
-        <v>7001581</v>
+        <v>7001570</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134067279</v>
+        <v>134067270</v>
       </c>
       <c r="B8" t="n">
-        <v>80481</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441523</v>
+        <v>441623</v>
       </c>
       <c r="R8" t="n">
-        <v>7001549</v>
+        <v>7001463</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134067267</v>
+        <v>134374945</v>
       </c>
       <c r="B9" t="n">
-        <v>92160</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västerfjället Ö, Jmt</t>
+          <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441542</v>
+        <v>441477</v>
       </c>
       <c r="R9" t="n">
-        <v>7001496</v>
+        <v>7001568</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,45 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134067272</v>
+        <v>134374946</v>
       </c>
       <c r="B10" t="n">
-        <v>92192</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västerfjället Ö, Jmt</t>
+          <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441565</v>
+        <v>441508</v>
       </c>
       <c r="R10" t="n">
-        <v>7001514</v>
+        <v>7001603</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1531,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134067269</v>
+        <v>134374947</v>
       </c>
       <c r="B11" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,14 +1579,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västerfjället Ö, Jmt</t>
+          <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441481</v>
+        <v>441572</v>
       </c>
       <c r="R11" t="n">
-        <v>7001570</v>
+        <v>7001497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1628,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134067284</v>
+        <v>134374948</v>
       </c>
       <c r="B12" t="n">
-        <v>89347</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,34 +1656,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västerfjället Ö, Jmt</t>
+          <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441493</v>
+        <v>441533</v>
       </c>
       <c r="R12" t="n">
-        <v>7001527</v>
+        <v>7001496</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1725,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134374945</v>
+        <v>134374949</v>
       </c>
       <c r="B13" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441477</v>
+        <v>441547</v>
       </c>
       <c r="R13" t="n">
-        <v>7001568</v>
+        <v>7001506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134374965</v>
+        <v>134374959</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>91988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441603</v>
+        <v>441508</v>
       </c>
       <c r="R14" t="n">
-        <v>7001485</v>
+        <v>7001539</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1910,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134374962</v>
+        <v>134374961</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>91988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441503</v>
+        <v>441512</v>
       </c>
       <c r="R15" t="n">
-        <v>7001567</v>
+        <v>7001546</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2027,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134374961</v>
+        <v>134374971</v>
       </c>
       <c r="B16" t="n">
-        <v>91981</v>
+        <v>83222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441512</v>
+        <v>441588</v>
       </c>
       <c r="R16" t="n">
-        <v>7001546</v>
+        <v>7001518</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134374948</v>
+        <v>134067267</v>
       </c>
       <c r="B17" t="n">
-        <v>91967</v>
+        <v>92167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,31 +2141,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västfjället Ö, Jmt</t>
+          <t>Västerfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441533</v>
+        <v>441542</v>
       </c>
       <c r="R17" t="n">
         <v>7001496</v>
@@ -2220,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134374970</v>
+        <v>134374944</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>92167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441501</v>
+        <v>441541</v>
       </c>
       <c r="R18" t="n">
-        <v>7001550</v>
+        <v>7001490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,11 +2298,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,45 +2324,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134374946</v>
+        <v>134067272</v>
       </c>
       <c r="B19" t="n">
-        <v>91967</v>
+        <v>92199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västfjället Ö, Jmt</t>
+          <t>Västerfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441508</v>
+        <v>441565</v>
       </c>
       <c r="R19" t="n">
-        <v>7001603</v>
+        <v>7001514</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2419,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2451,45 +2421,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134374956</v>
+        <v>134067281</v>
       </c>
       <c r="B20" t="n">
-        <v>99092</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västfjället Ö, Jmt</t>
+          <t>Västerfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441546</v>
+        <v>441484</v>
       </c>
       <c r="R20" t="n">
-        <v>7001525</v>
+        <v>7001581</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2516,12 +2486,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,45 +2523,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134374947</v>
+        <v>134067282</v>
       </c>
       <c r="B21" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västfjället Ö, Jmt</t>
+          <t>Västerfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441572</v>
+        <v>441505</v>
       </c>
       <c r="R21" t="n">
-        <v>7001497</v>
+        <v>7001580</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2613,12 +2588,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,45 +2625,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134374951</v>
+        <v>134067283</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Västfjället Ö, Jmt</t>
+          <t>Västerfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441506</v>
+        <v>441541</v>
       </c>
       <c r="R22" t="n">
-        <v>7001559</v>
+        <v>7001487</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2710,17 +2690,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2747,32 +2727,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134374974</v>
+        <v>134374962</v>
       </c>
       <c r="B23" t="n">
-        <v>89347</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2782,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441513</v>
+        <v>441503</v>
       </c>
       <c r="R23" t="n">
-        <v>7001578</v>
+        <v>7001567</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,6 +2798,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134374971</v>
+        <v>134374964</v>
       </c>
       <c r="B24" t="n">
-        <v>83215</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441588</v>
+        <v>441533</v>
       </c>
       <c r="R24" t="n">
-        <v>7001518</v>
+        <v>7001545</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,6 +2900,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2941,32 +2931,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134374959</v>
+        <v>134374965</v>
       </c>
       <c r="B25" t="n">
-        <v>91981</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441508</v>
+        <v>441603</v>
       </c>
       <c r="R25" t="n">
-        <v>7001539</v>
+        <v>7001485</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,6 +3002,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3038,14 +3033,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134374964</v>
+        <v>134374967</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3073,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441533</v>
+        <v>441623</v>
       </c>
       <c r="R26" t="n">
-        <v>7001545</v>
+        <v>7001479</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3143,11 +3138,11 @@
         <v>134374969</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3237,32 +3232,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134374955</v>
+        <v>134374970</v>
       </c>
       <c r="B28" t="n">
-        <v>99210</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3272,10 +3267,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441538</v>
+        <v>441501</v>
       </c>
       <c r="R28" t="n">
-        <v>7001492</v>
+        <v>7001550</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,6 +3303,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3334,10 +3334,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134374967</v>
+        <v>134067279</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,34 +3345,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västfjället Ö, Jmt</t>
+          <t>Västerfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441623</v>
+        <v>441523</v>
       </c>
       <c r="R29" t="n">
-        <v>7001479</v>
+        <v>7001549</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3399,17 +3399,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3436,10 +3431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134374949</v>
+        <v>134374951</v>
       </c>
       <c r="B30" t="n">
-        <v>91967</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3447,21 +3442,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441547</v>
+        <v>441506</v>
       </c>
       <c r="R30" t="n">
-        <v>7001506</v>
+        <v>7001559</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3507,6 +3502,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134374944</v>
+        <v>134374952</v>
       </c>
       <c r="B31" t="n">
-        <v>92160</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3544,34 +3544,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441541</v>
+        <v>441524</v>
       </c>
       <c r="R31" t="n">
-        <v>7001490</v>
+        <v>7001492</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,6 +3608,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3630,49 +3639,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134374952</v>
+        <v>134374956</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>99099</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441524</v>
+        <v>441546</v>
       </c>
       <c r="R32" t="n">
-        <v>7001492</v>
+        <v>7001525</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3707,11 +3712,6 @@
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3733,6 +3733,103 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134374955</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Västfjället Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>441538</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7001492</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21326-2026 artfynd.xlsx
+++ b/artfynd/A 21326-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3431,32 +3431,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134374951</v>
+        <v>134374956</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>99099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441506</v>
+        <v>441546</v>
       </c>
       <c r="R30" t="n">
-        <v>7001559</v>
+        <v>7001525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,11 +3502,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3533,46 +3528,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134374952</v>
+        <v>134374955</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>99217</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441524</v>
+        <v>441538</v>
       </c>
       <c r="R31" t="n">
         <v>7001492</v>
@@ -3610,11 +3601,6 @@
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3636,200 +3622,6 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>134374956</v>
-      </c>
-      <c r="B32" t="n">
-        <v>99099</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Corallorhiza trifida</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Västfjället Ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>441546</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7001525</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>134374955</v>
-      </c>
-      <c r="B33" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Västfjället Ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>441538</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7001492</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21326-2026 artfynd.xlsx
+++ b/artfynd/A 21326-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3431,32 +3431,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134374956</v>
+        <v>134374951</v>
       </c>
       <c r="B30" t="n">
-        <v>99099</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441546</v>
+        <v>441506</v>
       </c>
       <c r="R30" t="n">
-        <v>7001525</v>
+        <v>7001559</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,6 +3502,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3528,42 +3533,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134374955</v>
+        <v>134374952</v>
       </c>
       <c r="B31" t="n">
-        <v>99217</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441538</v>
+        <v>441524</v>
       </c>
       <c r="R31" t="n">
         <v>7001492</v>
@@ -3601,6 +3610,11 @@
           <t>2026-06-13</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3622,6 +3636,200 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134374956</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Västfjället Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>441546</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7001525</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134374955</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Västfjället Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>441538</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7001492</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
